--- a/case_studies/case_1/networks/existing/hydrogenPipelineOnshore.xlsx
+++ b/case_studies/case_1/networks/existing/hydrogenPipelineOnshore.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\case_1\networks\existing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800210AD-20C6-4132-9050-4F0CF9DAD533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87ACD9F-22FB-4256-833B-31015883CB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -881,22 +881,22 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -904,25 +904,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -930,25 +930,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -956,25 +956,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -982,25 +982,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1008,25 +1008,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1034,22 +1034,22 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>

--- a/case_studies/case_1/networks/existing/hydrogenPipelineOnshore.xlsx
+++ b/case_studies/case_1/networks/existing/hydrogenPipelineOnshore.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\case_1\networks\existing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C87ACD9F-22FB-4256-833B-31015883CB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B870AA-D5E0-47AE-B2F1-826A6687D8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -881,22 +881,22 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -904,25 +904,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -930,25 +930,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -956,25 +956,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -982,25 +982,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -1008,25 +1008,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1034,22 +1034,22 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="H8">
         <v>0</v>
